--- a/data/DATA_AST_LSI.xlsx
+++ b/data/DATA_AST_LSI.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Iftarr Hendry\Documents\annual_stock_take\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72FB41FC-D8A0-4C4D-B377-FCCBBDD8B815}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C25C89E9-D1A7-4C39-96C1-E3F5E559566C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{359B9B45-F88B-4FAF-99A8-60573E35A8DF}"/>
   </bookViews>
@@ -193,7 +193,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="325" uniqueCount="158">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="159">
   <si>
     <t>BATCH</t>
   </si>
@@ -668,6 +668,9 @@
   </si>
   <si>
     <t>kaisar rauf pasha</t>
+  </si>
+  <si>
+    <t>60023</t>
   </si>
 </sst>
 </file>
@@ -679,7 +682,7 @@
     <numFmt numFmtId="165" formatCode="#,##0;[Black]&quot;▲&quot;#,##0"/>
     <numFmt numFmtId="166" formatCode="#,##0.0;[Black]&quot;▲&quot;#,##0.0"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="11">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -749,6 +752,13 @@
       <color indexed="81"/>
       <name val="Tahoma"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="NanumBarunGothicOTF"/>
+      <family val="1"/>
+      <charset val="129"/>
     </font>
   </fonts>
   <fills count="6">
@@ -882,7 +892,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -983,9 +993,27 @@
     <xf numFmtId="16" fontId="6" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -998,22 +1026,13 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1421,7 +1440,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E9D3950-46A3-4710-8283-CFEB8F7F9459}">
-  <dimension ref="A1:P54"/>
+  <dimension ref="A1:P60"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="6.5546875" bestFit="1" customWidth="1"/>
@@ -1441,44 +1460,44 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="15">
-      <c r="A1" s="35" t="s">
+      <c r="A1" s="41" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="35" t="s">
+      <c r="B1" s="41" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="36" t="s">
+      <c r="C1" s="42" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="38" t="s">
+      <c r="D1" s="44" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="44">
+      <c r="E1" s="40">
         <v>2026</v>
       </c>
-      <c r="F1" s="44"/>
-      <c r="G1" s="44"/>
-      <c r="H1" s="41" t="s">
+      <c r="F1" s="40"/>
+      <c r="G1" s="40"/>
+      <c r="H1" s="37" t="s">
         <v>4</v>
       </c>
-      <c r="I1" s="41" t="s">
+      <c r="I1" s="37" t="s">
         <v>5</v>
       </c>
-      <c r="J1" s="42" t="s">
+      <c r="J1" s="38" t="s">
         <v>6</v>
       </c>
-      <c r="K1" s="43"/>
-      <c r="L1" s="43"/>
-      <c r="M1" s="43"/>
-      <c r="N1" s="43"/>
-      <c r="O1" s="43"/>
-      <c r="P1" s="43"/>
+      <c r="K1" s="39"/>
+      <c r="L1" s="39"/>
+      <c r="M1" s="39"/>
+      <c r="N1" s="39"/>
+      <c r="O1" s="39"/>
+      <c r="P1" s="39"/>
     </row>
     <row r="2" spans="1:16" ht="34.799999999999997">
-      <c r="A2" s="35"/>
-      <c r="B2" s="35"/>
-      <c r="C2" s="37"/>
-      <c r="D2" s="38"/>
+      <c r="A2" s="41"/>
+      <c r="B2" s="41"/>
+      <c r="C2" s="43"/>
+      <c r="D2" s="44"/>
       <c r="E2" s="1" t="s">
         <v>7</v>
       </c>
@@ -1488,8 +1507,8 @@
       <c r="G2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="H2" s="41"/>
-      <c r="I2" s="41"/>
+      <c r="H2" s="37"/>
+      <c r="I2" s="37"/>
       <c r="J2" s="3" t="s">
         <v>10</v>
       </c>
@@ -1531,7 +1550,7 @@
       <c r="P3" s="12"/>
     </row>
     <row r="4" spans="1:16" ht="15">
-      <c r="A4" s="39" t="s">
+      <c r="A4" s="34" t="s">
         <v>17</v>
       </c>
       <c r="B4" s="13" t="s">
@@ -1579,7 +1598,7 @@
       </c>
     </row>
     <row r="5" spans="1:16" ht="15">
-      <c r="A5" s="40"/>
+      <c r="A5" s="35"/>
       <c r="B5" s="13" t="s">
         <v>24</v>
       </c>
@@ -1693,7 +1712,7 @@
       </c>
     </row>
     <row r="8" spans="1:16" ht="15">
-      <c r="A8" s="39">
+      <c r="A8" s="34">
         <v>2</v>
       </c>
       <c r="B8" s="13" t="s">
@@ -1743,7 +1762,7 @@
       </c>
     </row>
     <row r="9" spans="1:16" ht="15">
-      <c r="A9" s="40"/>
+      <c r="A9" s="35"/>
       <c r="B9" s="13" t="s">
         <v>24</v>
       </c>
@@ -1809,17 +1828,17 @@
       <c r="P10" s="24"/>
     </row>
     <row r="11" spans="1:16" ht="15">
-      <c r="A11" s="34">
+      <c r="A11" s="36">
         <v>2</v>
       </c>
       <c r="B11" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="C11" s="13" t="s">
-        <v>47</v>
-      </c>
-      <c r="D11" s="26" t="s">
-        <v>48</v>
+      <c r="C11" s="14" t="s">
+        <v>62</v>
+      </c>
+      <c r="D11" s="45" t="s">
+        <v>63</v>
       </c>
       <c r="E11" s="16">
         <v>46314</v>
@@ -1837,37 +1856,37 @@
         <v>46329</v>
       </c>
       <c r="J11" s="19" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="K11" s="19" t="s">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="L11" s="19" t="s">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="M11" s="19" t="s">
         <v>51</v>
       </c>
       <c r="N11" s="20">
-        <v>-370</v>
+        <v>-700.12512500000003</v>
       </c>
       <c r="O11" s="20">
-        <v>-26</v>
+        <v>-1.8748749999999745</v>
       </c>
       <c r="P11" s="21">
-        <v>-6.5656565656565666</v>
+        <v>-0.26707621082620719</v>
       </c>
     </row>
     <row r="12" spans="1:16" ht="15">
-      <c r="A12" s="34"/>
+      <c r="A12" s="36"/>
       <c r="B12" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="C12" s="13" t="s">
-        <v>52</v>
+      <c r="C12" s="14" t="s">
+        <v>158</v>
       </c>
       <c r="D12" s="26" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E12" s="16">
         <v>46314</v>
@@ -1885,29 +1904,29 @@
         <v>46329</v>
       </c>
       <c r="J12" s="19" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="K12" s="19" t="s">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="L12" s="19" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="M12" s="19" t="s">
-        <v>46</v>
-      </c>
-      <c r="N12" s="25">
-        <v>-673</v>
+        <v>58</v>
+      </c>
+      <c r="N12" s="20">
+        <v>-599.39536959999998</v>
       </c>
       <c r="O12" s="20">
-        <v>477</v>
+        <v>-88.604630400000019</v>
       </c>
       <c r="P12" s="21">
-        <v>243.36734693877551</v>
+        <v>-12.878580000000003</v>
       </c>
     </row>
     <row r="13" spans="1:16" ht="15">
-      <c r="A13" s="34"/>
+      <c r="A13" s="36"/>
       <c r="B13" s="13" t="s">
         <v>24</v>
       </c>
@@ -1973,7 +1992,7 @@
       <c r="P14" s="24"/>
     </row>
     <row r="15" spans="1:16" ht="15">
-      <c r="A15" s="39">
+      <c r="A15" s="34">
         <v>3</v>
       </c>
       <c r="B15" s="13" t="s">
@@ -2023,15 +2042,15 @@
       </c>
     </row>
     <row r="16" spans="1:16" ht="15">
-      <c r="A16" s="40"/>
+      <c r="A16" s="35"/>
       <c r="B16" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="C16" s="13" t="s">
-        <v>62</v>
+      <c r="C16" s="14" t="s">
+        <v>47</v>
       </c>
       <c r="D16" s="26" t="s">
-        <v>63</v>
+        <v>48</v>
       </c>
       <c r="E16" s="16">
         <v>46319</v>
@@ -2049,25 +2068,25 @@
         <v>46334</v>
       </c>
       <c r="J16" s="19" t="s">
-        <v>64</v>
+        <v>49</v>
       </c>
       <c r="K16" s="19" t="s">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="L16" s="19" t="s">
-        <v>65</v>
+        <v>34</v>
       </c>
       <c r="M16" s="19" t="s">
         <v>51</v>
       </c>
       <c r="N16" s="20">
-        <v>-700.12512500000003</v>
+        <v>-370</v>
       </c>
       <c r="O16" s="20">
-        <v>-1.8748749999999745</v>
+        <v>-26</v>
       </c>
       <c r="P16" s="21">
-        <v>-0.26707621082620719</v>
+        <v>-6.5656565656565666</v>
       </c>
     </row>
     <row r="17" spans="1:16" ht="15">
@@ -2077,11 +2096,11 @@
       <c r="B17" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="C17" s="27">
-        <v>6023</v>
+      <c r="C17" s="47" t="s">
+        <v>52</v>
       </c>
       <c r="D17" s="26" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="E17" s="16">
         <v>46344</v>
@@ -2099,25 +2118,25 @@
         <v>46359</v>
       </c>
       <c r="J17" s="19" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="K17" s="19" t="s">
-        <v>56</v>
+        <v>30</v>
       </c>
       <c r="L17" s="19" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="M17" s="19" t="s">
-        <v>58</v>
-      </c>
-      <c r="N17" s="20">
-        <v>-599.39536959999998</v>
+        <v>46</v>
+      </c>
+      <c r="N17" s="25">
+        <v>-673</v>
       </c>
       <c r="O17" s="20">
-        <v>-88.604630400000019</v>
+        <v>477</v>
       </c>
       <c r="P17" s="21">
-        <v>-12.878580000000003</v>
+        <v>243.36734693877551</v>
       </c>
     </row>
     <row r="18" spans="1:16" ht="15">
@@ -2139,7 +2158,7 @@
       <c r="P18" s="24"/>
     </row>
     <row r="19" spans="1:16" ht="15">
-      <c r="A19" s="34">
+      <c r="A19" s="36">
         <v>3</v>
       </c>
       <c r="B19" s="13" t="s">
@@ -2189,7 +2208,7 @@
       </c>
     </row>
     <row r="20" spans="1:16" ht="15">
-      <c r="A20" s="34"/>
+      <c r="A20" s="36"/>
       <c r="B20" s="13" t="s">
         <v>24</v>
       </c>
@@ -2237,7 +2256,7 @@
       </c>
     </row>
     <row r="21" spans="1:16" ht="15">
-      <c r="A21" s="34"/>
+      <c r="A21" s="36"/>
       <c r="B21" s="13" t="s">
         <v>24</v>
       </c>
@@ -2303,7 +2322,7 @@
       <c r="P22" s="24"/>
     </row>
     <row r="23" spans="1:16" ht="15">
-      <c r="A23" s="34">
+      <c r="A23" s="36">
         <v>4</v>
       </c>
       <c r="B23" s="13" t="s">
@@ -2353,7 +2372,7 @@
       </c>
     </row>
     <row r="24" spans="1:16" ht="15">
-      <c r="A24" s="34"/>
+      <c r="A24" s="36"/>
       <c r="B24" s="13" t="s">
         <v>24</v>
       </c>
@@ -2401,7 +2420,7 @@
       </c>
     </row>
     <row r="25" spans="1:16" ht="15">
-      <c r="A25" s="34"/>
+      <c r="A25" s="36"/>
       <c r="B25" s="13" t="s">
         <v>24</v>
       </c>
@@ -2467,7 +2486,7 @@
       <c r="P26" s="24"/>
     </row>
     <row r="27" spans="1:16" ht="15">
-      <c r="A27" s="34">
+      <c r="A27" s="36">
         <v>5</v>
       </c>
       <c r="B27" s="13" t="s">
@@ -2517,7 +2536,7 @@
       </c>
     </row>
     <row r="28" spans="1:16" ht="15">
-      <c r="A28" s="34"/>
+      <c r="A28" s="36"/>
       <c r="B28" s="13" t="s">
         <v>24</v>
       </c>
@@ -2565,7 +2584,7 @@
       </c>
     </row>
     <row r="29" spans="1:16" ht="15">
-      <c r="A29" s="34"/>
+      <c r="A29" s="36"/>
       <c r="B29" s="13" t="s">
         <v>24</v>
       </c>
@@ -2631,7 +2650,7 @@
       <c r="P30" s="24"/>
     </row>
     <row r="31" spans="1:16" ht="15">
-      <c r="A31" s="34">
+      <c r="A31" s="36">
         <v>6</v>
       </c>
       <c r="B31" s="13" t="s">
@@ -2681,7 +2700,7 @@
       </c>
     </row>
     <row r="32" spans="1:16" ht="15">
-      <c r="A32" s="34"/>
+      <c r="A32" s="36"/>
       <c r="B32" s="13" t="s">
         <v>24</v>
       </c>
@@ -2729,7 +2748,7 @@
       </c>
     </row>
     <row r="33" spans="1:16" ht="15">
-      <c r="A33" s="34"/>
+      <c r="A33" s="36"/>
       <c r="B33" s="13" t="s">
         <v>24</v>
       </c>
@@ -2795,7 +2814,7 @@
       <c r="P34" s="24"/>
     </row>
     <row r="35" spans="1:16" ht="15">
-      <c r="A35" s="34">
+      <c r="A35" s="36">
         <v>7</v>
       </c>
       <c r="B35" s="13" t="s">
@@ -2845,7 +2864,7 @@
       </c>
     </row>
     <row r="36" spans="1:16" ht="15">
-      <c r="A36" s="34"/>
+      <c r="A36" s="36"/>
       <c r="B36" s="13" t="s">
         <v>24</v>
       </c>
@@ -2893,7 +2912,7 @@
       </c>
     </row>
     <row r="37" spans="1:16" ht="15">
-      <c r="A37" s="34"/>
+      <c r="A37" s="36"/>
       <c r="B37" s="13" t="s">
         <v>24</v>
       </c>
@@ -2959,7 +2978,7 @@
       <c r="P38" s="24"/>
     </row>
     <row r="39" spans="1:16" ht="15">
-      <c r="A39" s="34">
+      <c r="A39" s="36">
         <v>8</v>
       </c>
       <c r="B39" s="13" t="s">
@@ -3009,7 +3028,7 @@
       </c>
     </row>
     <row r="40" spans="1:16" ht="15">
-      <c r="A40" s="34"/>
+      <c r="A40" s="36"/>
       <c r="B40" s="13" t="s">
         <v>24</v>
       </c>
@@ -3057,7 +3076,7 @@
       </c>
     </row>
     <row r="41" spans="1:16" ht="15">
-      <c r="A41" s="34"/>
+      <c r="A41" s="36"/>
       <c r="B41" s="13" t="s">
         <v>24</v>
       </c>
@@ -3123,7 +3142,7 @@
       <c r="P42" s="24"/>
     </row>
     <row r="43" spans="1:16" ht="15">
-      <c r="A43" s="34">
+      <c r="A43" s="36">
         <v>9</v>
       </c>
       <c r="B43" s="13" t="s">
@@ -3173,7 +3192,7 @@
       </c>
     </row>
     <row r="44" spans="1:16" ht="15">
-      <c r="A44" s="34"/>
+      <c r="A44" s="36"/>
       <c r="B44" s="13" t="s">
         <v>24</v>
       </c>
@@ -3221,7 +3240,7 @@
       </c>
     </row>
     <row r="45" spans="1:16" ht="15">
-      <c r="A45" s="34"/>
+      <c r="A45" s="36"/>
       <c r="B45" s="13" t="s">
         <v>24</v>
       </c>
@@ -3287,7 +3306,7 @@
       <c r="P46" s="24"/>
     </row>
     <row r="47" spans="1:16" ht="15">
-      <c r="A47" s="34">
+      <c r="A47" s="36">
         <v>10</v>
       </c>
       <c r="B47" s="13" t="s">
@@ -3337,7 +3356,7 @@
       </c>
     </row>
     <row r="48" spans="1:16" ht="15">
-      <c r="A48" s="34"/>
+      <c r="A48" s="36"/>
       <c r="B48" s="13" t="s">
         <v>24</v>
       </c>
@@ -3385,7 +3404,7 @@
       </c>
     </row>
     <row r="49" spans="1:16" ht="15">
-      <c r="A49" s="34"/>
+      <c r="A49" s="36"/>
       <c r="B49" s="13" t="s">
         <v>24</v>
       </c>
@@ -3451,7 +3470,7 @@
       <c r="P50" s="24"/>
     </row>
     <row r="51" spans="1:16" ht="15">
-      <c r="A51" s="34">
+      <c r="A51" s="36">
         <v>11</v>
       </c>
       <c r="B51" s="13" t="s">
@@ -3501,7 +3520,7 @@
       </c>
     </row>
     <row r="52" spans="1:16" ht="15">
-      <c r="A52" s="34"/>
+      <c r="A52" s="36"/>
       <c r="B52" s="13" t="s">
         <v>24</v>
       </c>
@@ -3549,7 +3568,7 @@
       </c>
     </row>
     <row r="53" spans="1:16" ht="15">
-      <c r="A53" s="34"/>
+      <c r="A53" s="36"/>
       <c r="B53" s="13" t="s">
         <v>24</v>
       </c>
@@ -3614,8 +3633,87 @@
       <c r="O54" s="23"/>
       <c r="P54" s="24"/>
     </row>
+    <row r="56" spans="1:16" ht="15">
+      <c r="B56" s="13"/>
+      <c r="C56" s="13"/>
+      <c r="D56" s="46"/>
+      <c r="E56" s="16"/>
+      <c r="F56" s="17"/>
+      <c r="G56" s="18"/>
+      <c r="H56" s="17"/>
+      <c r="I56" s="17"/>
+      <c r="J56" s="19"/>
+      <c r="K56" s="19"/>
+      <c r="L56" s="19"/>
+      <c r="M56" s="19"/>
+      <c r="N56" s="20"/>
+      <c r="O56" s="20"/>
+      <c r="P56" s="21"/>
+    </row>
+    <row r="57" spans="1:16" ht="15">
+      <c r="B57" s="13"/>
+      <c r="C57" s="13"/>
+      <c r="E57" s="16"/>
+      <c r="F57" s="17"/>
+      <c r="G57" s="18"/>
+      <c r="H57" s="17"/>
+      <c r="I57" s="17"/>
+      <c r="J57" s="19"/>
+      <c r="K57" s="19"/>
+      <c r="L57" s="19"/>
+      <c r="M57" s="19"/>
+      <c r="N57" s="25"/>
+      <c r="O57" s="20"/>
+      <c r="P57" s="21"/>
+    </row>
+    <row r="59" spans="1:16" ht="15">
+      <c r="B59" s="13"/>
+      <c r="C59" s="13"/>
+      <c r="D59" s="46"/>
+      <c r="E59" s="16"/>
+      <c r="F59" s="17"/>
+      <c r="G59" s="18"/>
+      <c r="H59" s="17"/>
+      <c r="I59" s="17"/>
+      <c r="J59" s="19"/>
+      <c r="K59" s="19"/>
+      <c r="L59" s="19"/>
+      <c r="M59" s="19"/>
+      <c r="N59" s="20"/>
+      <c r="O59" s="20"/>
+      <c r="P59" s="21"/>
+    </row>
+    <row r="60" spans="1:16" ht="15">
+      <c r="B60" s="13"/>
+      <c r="C60" s="27"/>
+      <c r="D60" s="46"/>
+      <c r="E60" s="16"/>
+      <c r="F60" s="17"/>
+      <c r="G60" s="18"/>
+      <c r="H60" s="17"/>
+      <c r="I60" s="17"/>
+      <c r="J60" s="19"/>
+      <c r="K60" s="19"/>
+      <c r="L60" s="19"/>
+      <c r="M60" s="19"/>
+      <c r="N60" s="20"/>
+      <c r="O60" s="20"/>
+      <c r="P60" s="21"/>
+    </row>
   </sheetData>
   <mergeCells count="22">
+    <mergeCell ref="A11:A13"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:P1"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="E1:G1"/>
+    <mergeCell ref="H1:H2"/>
     <mergeCell ref="A15:A16"/>
     <mergeCell ref="A39:A41"/>
     <mergeCell ref="A43:A45"/>
@@ -3626,18 +3724,6 @@
     <mergeCell ref="A27:A29"/>
     <mergeCell ref="A31:A33"/>
     <mergeCell ref="A35:A37"/>
-    <mergeCell ref="I1:I2"/>
-    <mergeCell ref="J1:M1"/>
-    <mergeCell ref="N1:P1"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="E1:G1"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="A11:A13"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="A8:A9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -3645,7 +3731,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="10" operator="containsText" id="{1A0E45CE-F7AE-4D99-91A7-4F37B9FD5A27}">
+          <x14:cfRule type="containsText" priority="17" operator="containsText" id="{1A0E45CE-F7AE-4D99-91A7-4F37B9FD5A27}">
             <xm:f>NOT(ISERROR(SEARCH($D$2,A3)))</xm:f>
             <xm:f>$D$2</xm:f>
             <x14:dxf>
@@ -3656,11 +3742,11 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <xm:sqref>A18:P54 A3:P7 B9:F9 A10:P10 A11:F13 H11:P12 H13:I13 A8:F8 H8:P9 B16:P16 A14:P14 A15:I15 K15:P15 A17:I17</xm:sqref>
+          <xm:sqref>A3:P7 A8:F8 B9:F9 B16:I16 B57:C57 E57:P57 B56:P56</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="9" operator="containsText" id="{7E5347F1-C59B-49F2-A486-348876D00DDC}">
-            <xm:f>NOT(ISERROR(SEARCH($D$2,J13)))</xm:f>
+          <x14:cfRule type="containsText" priority="9" operator="containsText" id="{949D15F9-932E-41EA-B4DC-A7B149A7FBCA}">
+            <xm:f>NOT(ISERROR(SEARCH($D$2,A10)))</xm:f>
             <xm:f>$D$2</xm:f>
             <x14:dxf>
               <fill>
@@ -3670,11 +3756,11 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <xm:sqref>J13:P13</xm:sqref>
+          <xm:sqref>A10:P10 A13:P15 A11:I12</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="8" operator="containsText" id="{4F44122A-18C2-4992-B10B-86C31D8F76CE}">
-            <xm:f>NOT(ISERROR(SEARCH($D$2,G11)))</xm:f>
+          <x14:cfRule type="containsText" priority="8" operator="containsText" id="{4FB9DF6C-0043-478D-9ED6-EFE99F22D9A1}">
+            <xm:f>NOT(ISERROR(SEARCH($D$2,A17)))</xm:f>
             <xm:f>$D$2</xm:f>
             <x14:dxf>
               <fill>
@@ -3684,52 +3770,10 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <xm:sqref>G11</xm:sqref>
+          <xm:sqref>A18:P54 A17:I17</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="7" operator="containsText" id="{F210AB3F-B6EF-4F37-9D77-52D955C54013}">
-            <xm:f>NOT(ISERROR(SEARCH($D$2,G12)))</xm:f>
-            <xm:f>$D$2</xm:f>
-            <x14:dxf>
-              <fill>
-                <patternFill>
-                  <bgColor rgb="FFFFFF00"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>G12</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="6" operator="containsText" id="{975E79EC-1C64-4465-9393-7FF32A205188}">
-            <xm:f>NOT(ISERROR(SEARCH($D$2,G13)))</xm:f>
-            <xm:f>$D$2</xm:f>
-            <x14:dxf>
-              <fill>
-                <patternFill>
-                  <bgColor rgb="FFFFFF00"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>G13</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="5" operator="containsText" id="{06AB4D8A-DBC1-4013-AFD7-E3C16F8D4AD8}">
-            <xm:f>NOT(ISERROR(SEARCH($D$2,G9)))</xm:f>
-            <xm:f>$D$2</xm:f>
-            <x14:dxf>
-              <fill>
-                <patternFill>
-                  <bgColor rgb="FFFFFF00"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>G9</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="4" operator="containsText" id="{6EA13ADB-3188-4884-A67E-794CFD474769}">
+          <x14:cfRule type="containsText" priority="11" operator="containsText" id="{6EA13ADB-3188-4884-A67E-794CFD474769}">
             <xm:f>NOT(ISERROR(SEARCH($D$2,G8)))</xm:f>
             <xm:f>$D$2</xm:f>
             <x14:dxf>
@@ -3740,11 +3784,11 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <xm:sqref>G8</xm:sqref>
+          <xm:sqref>G8:P9</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="2" operator="containsText" id="{949D15F9-932E-41EA-B4DC-A7B149A7FBCA}">
-            <xm:f>NOT(ISERROR(SEARCH($D$2,J15)))</xm:f>
+          <x14:cfRule type="containsText" priority="6" operator="containsText" id="{D3EBB924-75D8-469B-8C3A-A8331CEF83C2}">
+            <xm:f>NOT(ISERROR(SEARCH($D$2,B59)))</xm:f>
             <xm:f>$D$2</xm:f>
             <x14:dxf>
               <fill>
@@ -3754,10 +3798,52 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <xm:sqref>J15</xm:sqref>
+          <xm:sqref>B59:P59</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="1" operator="containsText" id="{4FB9DF6C-0043-478D-9ED6-EFE99F22D9A1}">
+          <x14:cfRule type="containsText" priority="5" operator="containsText" id="{67CF2A4D-9843-4437-BE02-F20BF883A04D}">
+            <xm:f>NOT(ISERROR(SEARCH($D$2,B60)))</xm:f>
+            <xm:f>$D$2</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill>
+                  <bgColor rgb="FFFFFF00"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>B60:P60</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="containsText" priority="4" operator="containsText" id="{9E4CEA65-8C41-4231-A737-92A79332793E}">
+            <xm:f>NOT(ISERROR(SEARCH($D$2,J11)))</xm:f>
+            <xm:f>$D$2</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill>
+                  <bgColor rgb="FFFFFF00"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>J11:P11</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="containsText" priority="3" operator="containsText" id="{97C4B32D-80E9-4D03-AA73-7C7279B2EA70}">
+            <xm:f>NOT(ISERROR(SEARCH($D$2,J16)))</xm:f>
+            <xm:f>$D$2</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill>
+                  <bgColor rgb="FFFFFF00"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>J16:P16</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="containsText" priority="2" operator="containsText" id="{82203E34-7862-46AC-B05E-E4A35CE202DD}">
             <xm:f>NOT(ISERROR(SEARCH($D$2,J17)))</xm:f>
             <xm:f>$D$2</xm:f>
             <x14:dxf>
@@ -3770,6 +3856,20 @@
           </x14:cfRule>
           <xm:sqref>J17:P17</xm:sqref>
         </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="containsText" priority="1" operator="containsText" id="{C9F8E0B8-5BBA-4903-91BF-7F7022CD45AB}">
+            <xm:f>NOT(ISERROR(SEARCH($D$2,J12)))</xm:f>
+            <xm:f>$D$2</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill>
+                  <bgColor rgb="FFFFFF00"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>J12:P12</xm:sqref>
+        </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>
   </extLst>

--- a/data/DATA_AST_LSI.xlsx
+++ b/data/DATA_AST_LSI.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Iftarr Hendry\Documents\annual_stock_take\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C25C89E9-D1A7-4C39-96C1-E3F5E559566C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09CF8883-4B6C-481D-8796-9688AD4E7C62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{359B9B45-F88B-4FAF-99A8-60573E35A8DF}"/>
   </bookViews>
@@ -193,7 +193,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="159">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="160">
   <si>
     <t>BATCH</t>
   </si>
@@ -262,9 +262,6 @@
     <t>Rabu</t>
   </si>
   <si>
-    <t>Andri Setiadin (Commercial)</t>
-  </si>
-  <si>
     <t>-</t>
   </si>
   <si>
@@ -364,9 +361,6 @@
     <t>06023 - CIKARANG</t>
   </si>
   <si>
-    <t>Ryan (Comp)</t>
-  </si>
-  <si>
     <t>Erlangga (Logistic)</t>
   </si>
   <si>
@@ -379,9 +373,6 @@
     <t>06001 - PASAR REBO</t>
   </si>
   <si>
-    <t>Banu Oktriana (BRM)</t>
-  </si>
-  <si>
     <t>06004</t>
   </si>
   <si>
@@ -457,12 +448,6 @@
     <t>06037 - MATARAM</t>
   </si>
   <si>
-    <t>Asreza Yanuar (BRM)</t>
-  </si>
-  <si>
-    <t>Rosadi (Comp)</t>
-  </si>
-  <si>
     <t>06016</t>
   </si>
   <si>
@@ -502,9 +487,6 @@
     <t>Hadi suwarsono</t>
   </si>
   <si>
-    <t>Operation Strategy1</t>
-  </si>
-  <si>
     <t>Tendy (Ps Rebo)</t>
   </si>
   <si>
@@ -643,9 +625,6 @@
     <t>06038 - TEGAL</t>
   </si>
   <si>
-    <t>Operation Strategy2</t>
-  </si>
-  <si>
     <t>06027</t>
   </si>
   <si>
@@ -667,10 +646,34 @@
     <t>06039 - SERPONG</t>
   </si>
   <si>
-    <t>kaisar rauf pasha</t>
-  </si>
-  <si>
     <t>60023</t>
+  </si>
+  <si>
+    <t>Andri Setiadin (NF)</t>
+  </si>
+  <si>
+    <t>Risal Fauzi (NF)</t>
+  </si>
+  <si>
+    <t>Dwi Aryanto (Op Strat)</t>
+  </si>
+  <si>
+    <t>Ahmad Zaki (NF)</t>
+  </si>
+  <si>
+    <t>M Trisno Sanubari (LSI DF)</t>
+  </si>
+  <si>
+    <t>Dafa (Op Strat)</t>
+  </si>
+  <si>
+    <t>Royani</t>
+  </si>
+  <si>
+    <t>Rudi Syahreza (Cirebon)</t>
+  </si>
+  <si>
+    <t>Damar (ALC Alsut)</t>
   </si>
 </sst>
 </file>
@@ -993,15 +996,36 @@
     <xf numFmtId="16" fontId="6" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="164" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1012,34 +1036,251 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="10">
+  <dxfs count="44">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -1460,44 +1701,44 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="15">
-      <c r="A1" s="41" t="s">
+      <c r="A1" s="38" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="41" t="s">
+      <c r="B1" s="38" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="42" t="s">
+      <c r="C1" s="39" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="44" t="s">
+      <c r="D1" s="41" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="40">
+      <c r="E1" s="47">
         <v>2026</v>
       </c>
-      <c r="F1" s="40"/>
-      <c r="G1" s="40"/>
-      <c r="H1" s="37" t="s">
+      <c r="F1" s="47"/>
+      <c r="G1" s="47"/>
+      <c r="H1" s="44" t="s">
         <v>4</v>
       </c>
-      <c r="I1" s="37" t="s">
+      <c r="I1" s="44" t="s">
         <v>5</v>
       </c>
-      <c r="J1" s="38" t="s">
+      <c r="J1" s="45" t="s">
         <v>6</v>
       </c>
-      <c r="K1" s="39"/>
-      <c r="L1" s="39"/>
-      <c r="M1" s="39"/>
-      <c r="N1" s="39"/>
-      <c r="O1" s="39"/>
-      <c r="P1" s="39"/>
+      <c r="K1" s="46"/>
+      <c r="L1" s="46"/>
+      <c r="M1" s="46"/>
+      <c r="N1" s="46"/>
+      <c r="O1" s="46"/>
+      <c r="P1" s="46"/>
     </row>
     <row r="2" spans="1:16" ht="34.799999999999997">
-      <c r="A2" s="41"/>
-      <c r="B2" s="41"/>
-      <c r="C2" s="43"/>
-      <c r="D2" s="44"/>
+      <c r="A2" s="38"/>
+      <c r="B2" s="38"/>
+      <c r="C2" s="40"/>
+      <c r="D2" s="41"/>
       <c r="E2" s="1" t="s">
         <v>7</v>
       </c>
@@ -1507,8 +1748,8 @@
       <c r="G2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="H2" s="37"/>
-      <c r="I2" s="37"/>
+      <c r="H2" s="44"/>
+      <c r="I2" s="44"/>
       <c r="J2" s="3" t="s">
         <v>10</v>
       </c>
@@ -1550,7 +1791,7 @@
       <c r="P3" s="12"/>
     </row>
     <row r="4" spans="1:16" ht="15">
-      <c r="A4" s="34" t="s">
+      <c r="A4" s="42" t="s">
         <v>17</v>
       </c>
       <c r="B4" s="13" t="s">
@@ -1567,7 +1808,7 @@
         <v>46322</v>
       </c>
       <c r="G4" s="18" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="H4" s="17">
         <v>46322</v>
@@ -1576,44 +1817,44 @@
         <v>46322</v>
       </c>
       <c r="J4" s="19" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="K4" s="19" t="s">
+        <v>151</v>
+      </c>
+      <c r="L4" s="19" t="s">
         <v>22</v>
       </c>
-      <c r="L4" s="19" t="s">
-        <v>23</v>
-      </c>
       <c r="M4" s="19" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N4" s="20" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O4" s="20" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="P4" s="21">
         <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:16" ht="15">
-      <c r="A5" s="35"/>
+      <c r="A5" s="43"/>
       <c r="B5" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="C5" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="C5" s="14" t="s">
+      <c r="D5" s="15" t="s">
         <v>25</v>
-      </c>
-      <c r="D5" s="15" t="s">
-        <v>26</v>
       </c>
       <c r="E5" s="16"/>
       <c r="F5" s="17">
         <v>46328</v>
       </c>
       <c r="G5" s="18" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H5" s="17">
         <v>46328</v>
@@ -1622,22 +1863,22 @@
         <v>46328</v>
       </c>
       <c r="J5" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="K5" s="19" t="s">
         <v>28</v>
       </c>
-      <c r="K5" s="19" t="s">
-        <v>29</v>
-      </c>
-      <c r="L5" s="22" t="s">
-        <v>30</v>
+      <c r="L5" s="19" t="s">
+        <v>53</v>
       </c>
       <c r="M5" s="19" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N5" s="20" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O5" s="20" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="P5" s="21">
         <v>0</v>
@@ -1666,13 +1907,13 @@
         <v>1</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C7" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="D7" s="15" t="s">
         <v>31</v>
-      </c>
-      <c r="D7" s="15" t="s">
-        <v>32</v>
       </c>
       <c r="E7" s="16">
         <v>46302</v>
@@ -1690,16 +1931,16 @@
         <v>46317</v>
       </c>
       <c r="J7" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="K7" s="19" t="s">
+        <v>106</v>
+      </c>
+      <c r="L7" s="19" t="s">
         <v>33</v>
       </c>
-      <c r="K7" s="19" t="s">
-        <v>34</v>
-      </c>
-      <c r="L7" s="19" t="s">
-        <v>35</v>
-      </c>
       <c r="M7" s="19" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="N7" s="20">
         <v>-200</v>
@@ -1712,17 +1953,17 @@
       </c>
     </row>
     <row r="8" spans="1:16" ht="15">
-      <c r="A8" s="34">
+      <c r="A8" s="42">
         <v>2</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C8" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="D8" s="15" t="s">
         <v>37</v>
-      </c>
-      <c r="D8" s="15" t="s">
-        <v>38</v>
       </c>
       <c r="E8" s="16">
         <v>46314</v>
@@ -1731,7 +1972,7 @@
         <v>46328</v>
       </c>
       <c r="G8" s="18" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H8" s="17">
         <v>46326</v>
@@ -1740,16 +1981,16 @@
         <v>46329</v>
       </c>
       <c r="J8" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="K8" s="19" t="s">
         <v>39</v>
       </c>
-      <c r="K8" s="19" t="s">
+      <c r="L8" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="M8" s="19" t="s">
         <v>40</v>
-      </c>
-      <c r="L8" s="22" t="s">
-        <v>30</v>
-      </c>
-      <c r="M8" s="19" t="s">
-        <v>41</v>
       </c>
       <c r="N8" s="25">
         <v>-310</v>
@@ -1762,15 +2003,15 @@
       </c>
     </row>
     <row r="9" spans="1:16" ht="15">
-      <c r="A9" s="35"/>
+      <c r="A9" s="43"/>
       <c r="B9" s="13" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C9" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="D9" s="15" t="s">
         <v>42</v>
-      </c>
-      <c r="D9" s="15" t="s">
-        <v>43</v>
       </c>
       <c r="E9" s="16">
         <v>46314</v>
@@ -1779,7 +2020,7 @@
         <v>46328</v>
       </c>
       <c r="G9" s="18" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H9" s="17">
         <v>46326</v>
@@ -1788,16 +2029,16 @@
         <v>46329</v>
       </c>
       <c r="J9" s="19" t="s">
+        <v>106</v>
+      </c>
+      <c r="K9" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="L9" s="19" t="s">
         <v>44</v>
       </c>
-      <c r="K9" s="19" t="s">
-        <v>29</v>
-      </c>
-      <c r="L9" s="19" t="s">
-        <v>45</v>
-      </c>
       <c r="M9" s="19" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="N9" s="20">
         <v>-602</v>
@@ -1828,17 +2069,17 @@
       <c r="P10" s="24"/>
     </row>
     <row r="11" spans="1:16" ht="15">
-      <c r="A11" s="36">
+      <c r="A11" s="37">
         <v>2</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C11" s="14" t="s">
-        <v>62</v>
-      </c>
-      <c r="D11" s="45" t="s">
-        <v>63</v>
+        <v>59</v>
+      </c>
+      <c r="D11" s="34" t="s">
+        <v>60</v>
       </c>
       <c r="E11" s="16">
         <v>46314</v>
@@ -1847,7 +2088,7 @@
         <v>46328</v>
       </c>
       <c r="G11" s="18" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H11" s="17">
         <v>46326</v>
@@ -1856,16 +2097,16 @@
         <v>46329</v>
       </c>
       <c r="J11" s="19" t="s">
-        <v>64</v>
+        <v>43</v>
       </c>
       <c r="K11" s="19" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="L11" s="19" t="s">
-        <v>65</v>
+        <v>115</v>
       </c>
       <c r="M11" s="19" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="N11" s="20">
         <v>-700.12512500000003</v>
@@ -1878,15 +2119,15 @@
       </c>
     </row>
     <row r="12" spans="1:16" ht="15">
-      <c r="A12" s="36"/>
+      <c r="A12" s="37"/>
       <c r="B12" s="13" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C12" s="14" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
       <c r="D12" s="26" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E12" s="16">
         <v>46314</v>
@@ -1895,7 +2136,7 @@
         <v>46328</v>
       </c>
       <c r="G12" s="18" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H12" s="17">
         <v>46326</v>
@@ -1904,16 +2145,16 @@
         <v>46329</v>
       </c>
       <c r="J12" s="19" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="K12" s="19" t="s">
-        <v>56</v>
+        <v>130</v>
       </c>
       <c r="L12" s="19" t="s">
-        <v>57</v>
+        <v>152</v>
       </c>
       <c r="M12" s="19" t="s">
-        <v>58</v>
+        <v>133</v>
       </c>
       <c r="N12" s="20">
         <v>-599.39536959999998</v>
@@ -1926,15 +2167,15 @@
       </c>
     </row>
     <row r="13" spans="1:16" ht="15">
-      <c r="A13" s="36"/>
+      <c r="A13" s="37"/>
       <c r="B13" s="13" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C13" s="27" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="D13" s="26" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="E13" s="16">
         <v>46314</v>
@@ -1943,7 +2184,7 @@
         <v>46328</v>
       </c>
       <c r="G13" s="18" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H13" s="17">
         <v>46326</v>
@@ -1952,16 +2193,16 @@
         <v>46329</v>
       </c>
       <c r="J13" s="19" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="K13" s="19" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="L13" s="19" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="M13" s="19" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="N13" s="20">
         <v>-115</v>
@@ -1992,17 +2233,17 @@
       <c r="P14" s="24"/>
     </row>
     <row r="15" spans="1:16" ht="15">
-      <c r="A15" s="34">
+      <c r="A15" s="42">
         <v>3</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C15" s="13" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D15" s="26" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E15" s="16">
         <v>46319</v>
@@ -2011,7 +2252,7 @@
         <v>46333</v>
       </c>
       <c r="G15" s="18" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="H15" s="17">
         <v>46331</v>
@@ -2020,16 +2261,16 @@
         <v>46334</v>
       </c>
       <c r="J15" s="19" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K15" s="19" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="L15" s="19" t="s">
-        <v>34</v>
+        <v>127</v>
       </c>
       <c r="M15" s="19" t="s">
-        <v>61</v>
+        <v>153</v>
       </c>
       <c r="N15" s="25">
         <v>-1300</v>
@@ -2042,15 +2283,15 @@
       </c>
     </row>
     <row r="16" spans="1:16" ht="15">
-      <c r="A16" s="35"/>
+      <c r="A16" s="43"/>
       <c r="B16" s="13" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C16" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="D16" s="26" t="s">
         <v>47</v>
-      </c>
-      <c r="D16" s="26" t="s">
-        <v>48</v>
       </c>
       <c r="E16" s="16">
         <v>46319</v>
@@ -2059,7 +2300,7 @@
         <v>46333</v>
       </c>
       <c r="G16" s="18" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="H16" s="17">
         <v>46331</v>
@@ -2068,16 +2309,16 @@
         <v>46334</v>
       </c>
       <c r="J16" s="19" t="s">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="K16" s="19" t="s">
+        <v>33</v>
+      </c>
+      <c r="L16" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="M16" s="19" t="s">
         <v>50</v>
-      </c>
-      <c r="L16" s="19" t="s">
-        <v>34</v>
-      </c>
-      <c r="M16" s="19" t="s">
-        <v>51</v>
       </c>
       <c r="N16" s="20">
         <v>-370</v>
@@ -2094,13 +2335,13 @@
         <v>7</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="C17" s="47" t="s">
+        <v>23</v>
+      </c>
+      <c r="C17" s="36" t="s">
+        <v>51</v>
+      </c>
+      <c r="D17" s="26" t="s">
         <v>52</v>
-      </c>
-      <c r="D17" s="26" t="s">
-        <v>53</v>
       </c>
       <c r="E17" s="16">
         <v>46344</v>
@@ -2118,16 +2359,16 @@
         <v>46359</v>
       </c>
       <c r="J17" s="19" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="K17" s="19" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="L17" s="19" t="s">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="M17" s="19" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="N17" s="25">
         <v>-673</v>
@@ -2158,17 +2399,17 @@
       <c r="P18" s="24"/>
     </row>
     <row r="19" spans="1:16" ht="15">
-      <c r="A19" s="36">
+      <c r="A19" s="37">
         <v>3</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C19" s="13" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="D19" s="15" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="E19" s="16">
         <v>46319</v>
@@ -2177,7 +2418,7 @@
         <v>46333</v>
       </c>
       <c r="G19" s="18" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="H19" s="17">
         <v>46331</v>
@@ -2186,16 +2427,16 @@
         <v>46334</v>
       </c>
       <c r="J19" s="19" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="K19" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="L19" s="19" t="s">
         <v>40</v>
       </c>
-      <c r="L19" s="19" t="s">
-        <v>74</v>
-      </c>
       <c r="M19" s="19" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="N19" s="20">
         <v>-225</v>
@@ -2208,15 +2449,15 @@
       </c>
     </row>
     <row r="20" spans="1:16" ht="15">
-      <c r="A20" s="36"/>
+      <c r="A20" s="37"/>
       <c r="B20" s="13" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C20" s="13" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="D20" s="26" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="E20" s="16">
         <v>46319</v>
@@ -2225,7 +2466,7 @@
         <v>46333</v>
       </c>
       <c r="G20" s="18" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="H20" s="17">
         <v>46331</v>
@@ -2234,16 +2475,16 @@
         <v>46334</v>
       </c>
       <c r="J20" s="19" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="K20" s="19" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="L20" s="19" t="s">
-        <v>36</v>
+        <v>71</v>
       </c>
       <c r="M20" s="19" t="s">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="N20" s="20">
         <v>-155</v>
@@ -2256,15 +2497,15 @@
       </c>
     </row>
     <row r="21" spans="1:16" ht="15">
-      <c r="A21" s="36"/>
+      <c r="A21" s="37"/>
       <c r="B21" s="13" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C21" s="27" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D21" s="26" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="E21" s="16">
         <v>46319</v>
@@ -2273,7 +2514,7 @@
         <v>46333</v>
       </c>
       <c r="G21" s="18" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="H21" s="17">
         <v>46331</v>
@@ -2282,16 +2523,16 @@
         <v>46334</v>
       </c>
       <c r="J21" s="19" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="K21" s="19" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="L21" s="19" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="M21" s="19" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="N21" s="20">
         <v>-420</v>
@@ -2322,17 +2563,17 @@
       <c r="P22" s="24"/>
     </row>
     <row r="23" spans="1:16" ht="15">
-      <c r="A23" s="36">
+      <c r="A23" s="37">
         <v>4</v>
       </c>
       <c r="B23" s="13" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C23" s="13" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D23" s="15" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="E23" s="16">
         <v>46324</v>
@@ -2341,7 +2582,7 @@
         <v>46338</v>
       </c>
       <c r="G23" s="18" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="H23" s="17">
         <v>46336</v>
@@ -2350,16 +2591,16 @@
         <v>46339</v>
       </c>
       <c r="J23" s="19" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="K23" s="19" t="s">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="L23" s="19" t="s">
-        <v>74</v>
+        <v>62</v>
       </c>
       <c r="M23" s="19" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="N23" s="20">
         <v>-155.38490890649999</v>
@@ -2372,15 +2613,15 @@
       </c>
     </row>
     <row r="24" spans="1:16" ht="15">
-      <c r="A24" s="36"/>
+      <c r="A24" s="37"/>
       <c r="B24" s="13" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C24" s="13" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="D24" s="15" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="E24" s="16">
         <v>46324</v>
@@ -2389,7 +2630,7 @@
         <v>46338</v>
       </c>
       <c r="G24" s="18" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="H24" s="17">
         <v>46336</v>
@@ -2398,16 +2639,16 @@
         <v>46339</v>
       </c>
       <c r="J24" s="19" t="s">
-        <v>87</v>
+        <v>32</v>
       </c>
       <c r="K24" s="19" t="s">
         <v>33</v>
       </c>
       <c r="L24" s="19" t="s">
-        <v>34</v>
+        <v>154</v>
       </c>
       <c r="M24" s="19" t="s">
-        <v>88</v>
+        <v>155</v>
       </c>
       <c r="N24" s="25">
         <v>-771.12590870899999</v>
@@ -2420,15 +2661,15 @@
       </c>
     </row>
     <row r="25" spans="1:16" ht="15">
-      <c r="A25" s="36"/>
+      <c r="A25" s="37"/>
       <c r="B25" s="13" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C25" s="28" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="D25" s="29" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="E25" s="16">
         <v>46324</v>
@@ -2437,7 +2678,7 @@
         <v>46338</v>
       </c>
       <c r="G25" s="18" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="H25" s="17">
         <v>46336</v>
@@ -2446,16 +2687,16 @@
         <v>46339</v>
       </c>
       <c r="J25" s="19" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K25" s="19" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="L25" s="19" t="s">
-        <v>91</v>
+        <v>140</v>
       </c>
       <c r="M25" s="19" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="N25" s="20">
         <v>-356</v>
@@ -2486,17 +2727,17 @@
       <c r="P26" s="24"/>
     </row>
     <row r="27" spans="1:16" ht="15">
-      <c r="A27" s="36">
+      <c r="A27" s="37">
         <v>5</v>
       </c>
       <c r="B27" s="13" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C27" s="30" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="D27" s="15" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="E27" s="16">
         <v>46331</v>
@@ -2505,7 +2746,7 @@
         <v>46345</v>
       </c>
       <c r="G27" s="18" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="H27" s="17">
         <v>46343</v>
@@ -2514,16 +2755,16 @@
         <v>46346</v>
       </c>
       <c r="J27" s="19" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="K27" s="19" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="L27" s="19" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="M27" s="19" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="N27" s="20">
         <v>-180</v>
@@ -2536,15 +2777,15 @@
       </c>
     </row>
     <row r="28" spans="1:16" ht="15">
-      <c r="A28" s="36"/>
+      <c r="A28" s="37"/>
       <c r="B28" s="13" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C28" s="30" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="D28" s="15" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="E28" s="16">
         <v>46331</v>
@@ -2553,7 +2794,7 @@
         <v>46345</v>
       </c>
       <c r="G28" s="18" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="H28" s="17">
         <v>46343</v>
@@ -2562,16 +2803,16 @@
         <v>46346</v>
       </c>
       <c r="J28" s="19" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="K28" s="19" t="s">
-        <v>61</v>
+        <v>28</v>
       </c>
       <c r="L28" s="19" t="s">
-        <v>29</v>
+        <v>155</v>
       </c>
       <c r="M28" s="19" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="N28" s="25">
         <v>-606</v>
@@ -2584,15 +2825,15 @@
       </c>
     </row>
     <row r="29" spans="1:16" ht="15">
-      <c r="A29" s="36"/>
+      <c r="A29" s="37"/>
       <c r="B29" s="13" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C29" s="13" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="D29" s="15" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="E29" s="16">
         <v>46331</v>
@@ -2601,7 +2842,7 @@
         <v>46345</v>
       </c>
       <c r="G29" s="18" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="H29" s="17">
         <v>46343</v>
@@ -2610,16 +2851,16 @@
         <v>46346</v>
       </c>
       <c r="J29" s="19" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="K29" s="19" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="L29" s="19" t="s">
-        <v>102</v>
+        <v>29</v>
       </c>
       <c r="M29" s="19" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="N29" s="25">
         <v>-832.12498769089996</v>
@@ -2650,17 +2891,17 @@
       <c r="P30" s="24"/>
     </row>
     <row r="31" spans="1:16" ht="15">
-      <c r="A31" s="36">
+      <c r="A31" s="37">
         <v>6</v>
       </c>
       <c r="B31" s="13" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C31" s="13" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="D31" s="15" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="E31" s="16">
         <v>46338</v>
@@ -2669,7 +2910,7 @@
         <v>46352</v>
       </c>
       <c r="G31" s="18" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="H31" s="17">
         <v>46350</v>
@@ -2678,16 +2919,16 @@
         <v>46353</v>
       </c>
       <c r="J31" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="K31" s="19" t="s">
         <v>40</v>
       </c>
-      <c r="K31" s="19" t="s">
-        <v>41</v>
-      </c>
       <c r="L31" s="19" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="M31" s="19" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="N31" s="20">
         <v>-250</v>
@@ -2700,15 +2941,15 @@
       </c>
     </row>
     <row r="32" spans="1:16" ht="15">
-      <c r="A32" s="36"/>
+      <c r="A32" s="37"/>
       <c r="B32" s="13" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C32" s="13" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="D32" s="26" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="E32" s="16">
         <v>46338</v>
@@ -2717,7 +2958,7 @@
         <v>46352</v>
       </c>
       <c r="G32" s="18" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="H32" s="17">
         <v>46350</v>
@@ -2726,16 +2967,16 @@
         <v>46353</v>
       </c>
       <c r="J32" s="19" t="s">
-        <v>87</v>
+        <v>32</v>
       </c>
       <c r="K32" s="19" t="s">
-        <v>88</v>
+        <v>156</v>
       </c>
       <c r="L32" s="19" t="s">
-        <v>33</v>
+        <v>133</v>
       </c>
       <c r="M32" s="19" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="N32" s="20">
         <v>-652.90306899999996</v>
@@ -2748,15 +2989,15 @@
       </c>
     </row>
     <row r="33" spans="1:16" ht="15">
-      <c r="A33" s="36"/>
+      <c r="A33" s="37"/>
       <c r="B33" s="13" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C33" s="13" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="D33" s="26" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="E33" s="16">
         <v>46338</v>
@@ -2765,7 +3006,7 @@
         <v>46352</v>
       </c>
       <c r="G33" s="18" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="H33" s="17">
         <v>46350</v>
@@ -2774,16 +3015,16 @@
         <v>46353</v>
       </c>
       <c r="J33" s="19" t="s">
-        <v>112</v>
+        <v>49</v>
       </c>
       <c r="K33" s="19" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="L33" s="19" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="M33" s="19" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="N33" s="20">
         <v>-395</v>
@@ -2814,17 +3055,17 @@
       <c r="P34" s="24"/>
     </row>
     <row r="35" spans="1:16" ht="15">
-      <c r="A35" s="36">
+      <c r="A35" s="37">
         <v>7</v>
       </c>
       <c r="B35" s="13" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C35" s="30" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="D35" s="26" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="E35" s="16">
         <v>46344</v>
@@ -2842,16 +3083,16 @@
         <v>46359</v>
       </c>
       <c r="J35" s="19" t="s">
-        <v>87</v>
+        <v>61</v>
       </c>
       <c r="K35" s="19" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="L35" s="19" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="M35" s="19" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="N35" s="20">
         <v>-365</v>
@@ -2864,15 +3105,15 @@
       </c>
     </row>
     <row r="36" spans="1:16" ht="15">
-      <c r="A36" s="36"/>
+      <c r="A36" s="37"/>
       <c r="B36" s="13" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C36" s="30" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="D36" s="26" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="E36" s="16">
         <v>46344</v>
@@ -2890,16 +3131,16 @@
         <v>46359</v>
       </c>
       <c r="J36" s="19" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K36" s="19" t="s">
+        <v>157</v>
+      </c>
+      <c r="L36" s="19" t="s">
+        <v>86</v>
+      </c>
+      <c r="M36" s="19" t="s">
         <v>112</v>
-      </c>
-      <c r="L36" s="19" t="s">
-        <v>91</v>
-      </c>
-      <c r="M36" s="19" t="s">
-        <v>118</v>
       </c>
       <c r="N36" s="20">
         <v>-812.23404271999993</v>
@@ -2912,15 +3153,15 @@
       </c>
     </row>
     <row r="37" spans="1:16" ht="15">
-      <c r="A37" s="36"/>
+      <c r="A37" s="37"/>
       <c r="B37" s="13" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C37" s="13" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="D37" s="26" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="E37" s="16">
         <v>46344</v>
@@ -2938,16 +3179,16 @@
         <v>46359</v>
       </c>
       <c r="J37" s="19" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="K37" s="19" t="s">
-        <v>64</v>
+        <v>29</v>
       </c>
       <c r="L37" s="19" t="s">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="M37" s="19" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="N37" s="20">
         <v>-175</v>
@@ -2978,17 +3219,17 @@
       <c r="P38" s="24"/>
     </row>
     <row r="39" spans="1:16" ht="15">
-      <c r="A39" s="36">
+      <c r="A39" s="37">
         <v>8</v>
       </c>
       <c r="B39" s="13" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C39" s="30" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="D39" s="26" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="E39" s="16">
         <v>46349</v>
@@ -2997,7 +3238,7 @@
         <v>46363</v>
       </c>
       <c r="G39" s="18" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H39" s="17">
         <v>46361</v>
@@ -3006,16 +3247,16 @@
         <v>46364</v>
       </c>
       <c r="J39" s="19" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K39" s="19" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="L39" s="19" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="M39" s="19" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="N39" s="20">
         <v>-207.39551349999999</v>
@@ -3028,15 +3269,15 @@
       </c>
     </row>
     <row r="40" spans="1:16" ht="15">
-      <c r="A40" s="36"/>
+      <c r="A40" s="37"/>
       <c r="B40" s="13" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C40" s="13" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="D40" s="15" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="E40" s="16">
         <v>46349</v>
@@ -3045,7 +3286,7 @@
         <v>46363</v>
       </c>
       <c r="G40" s="18" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H40" s="17">
         <v>46361</v>
@@ -3054,16 +3295,16 @@
         <v>46364</v>
       </c>
       <c r="J40" s="19" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="K40" s="19" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="L40" s="19" t="s">
-        <v>88</v>
+        <v>130</v>
       </c>
       <c r="M40" s="19" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="N40" s="20">
         <v>-224</v>
@@ -3076,15 +3317,15 @@
       </c>
     </row>
     <row r="41" spans="1:16" ht="15">
-      <c r="A41" s="36"/>
+      <c r="A41" s="37"/>
       <c r="B41" s="13" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C41" s="30" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="D41" s="26" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="E41" s="16">
         <v>46349</v>
@@ -3093,7 +3334,7 @@
         <v>46363</v>
       </c>
       <c r="G41" s="18" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H41" s="17">
         <v>46361</v>
@@ -3102,16 +3343,16 @@
         <v>46364</v>
       </c>
       <c r="J41" s="19" t="s">
-        <v>87</v>
+        <v>61</v>
       </c>
       <c r="K41" s="19" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="L41" s="19" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="M41" s="19" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="N41" s="20">
         <v>-403</v>
@@ -3142,17 +3383,17 @@
       <c r="P42" s="24"/>
     </row>
     <row r="43" spans="1:16" ht="15">
-      <c r="A43" s="36">
+      <c r="A43" s="37">
         <v>9</v>
       </c>
       <c r="B43" s="13" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C43" s="13" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="D43" s="15" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="E43" s="16">
         <v>46354</v>
@@ -3161,7 +3402,7 @@
         <v>46368</v>
       </c>
       <c r="G43" s="18" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="H43" s="17">
         <v>46366</v>
@@ -3170,16 +3411,16 @@
         <v>46369</v>
       </c>
       <c r="J43" s="19" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="K43" s="19" t="s">
-        <v>33</v>
+        <v>152</v>
       </c>
       <c r="L43" s="19" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="M43" s="19" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="N43" s="20">
         <v>-636.85758020000003</v>
@@ -3192,15 +3433,15 @@
       </c>
     </row>
     <row r="44" spans="1:16" ht="15">
-      <c r="A44" s="36"/>
+      <c r="A44" s="37"/>
       <c r="B44" s="13" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C44" s="13" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="D44" s="15" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="E44" s="16">
         <v>46354</v>
@@ -3209,7 +3450,7 @@
         <v>46368</v>
       </c>
       <c r="G44" s="18" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="H44" s="17">
         <v>46366</v>
@@ -3218,16 +3459,16 @@
         <v>46369</v>
       </c>
       <c r="J44" s="19" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K44" s="19" t="s">
-        <v>64</v>
+        <v>154</v>
       </c>
       <c r="L44" s="19" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="M44" s="19" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="N44" s="20">
         <v>-519.06560846000002</v>
@@ -3240,15 +3481,15 @@
       </c>
     </row>
     <row r="45" spans="1:16" ht="15">
-      <c r="A45" s="36"/>
+      <c r="A45" s="37"/>
       <c r="B45" s="13" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C45" s="13" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="D45" s="15" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="E45" s="16">
         <v>46354</v>
@@ -3257,7 +3498,7 @@
         <v>46368</v>
       </c>
       <c r="G45" s="18" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="H45" s="17">
         <v>46366</v>
@@ -3266,16 +3507,16 @@
         <v>46369</v>
       </c>
       <c r="J45" s="19" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="K45" s="19" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="L45" s="19" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="M45" s="19" t="s">
-        <v>102</v>
+        <v>153</v>
       </c>
       <c r="N45" s="25">
         <v>-1200</v>
@@ -3306,17 +3547,17 @@
       <c r="P46" s="24"/>
     </row>
     <row r="47" spans="1:16" ht="15">
-      <c r="A47" s="36">
+      <c r="A47" s="37">
         <v>10</v>
       </c>
       <c r="B47" s="13" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C47" s="16" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="D47" s="33" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="E47" s="16">
         <v>46359</v>
@@ -3325,7 +3566,7 @@
         <v>46373</v>
       </c>
       <c r="G47" s="18" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="H47" s="17">
         <v>46371</v>
@@ -3334,16 +3575,16 @@
         <v>46374</v>
       </c>
       <c r="J47" s="19" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="K47" s="19" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="L47" s="19" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="M47" s="19" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="N47" s="20">
         <v>-344.185765</v>
@@ -3356,15 +3597,15 @@
       </c>
     </row>
     <row r="48" spans="1:16" ht="15">
-      <c r="A48" s="36"/>
+      <c r="A48" s="37"/>
       <c r="B48" s="13" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C48" s="13" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="D48" s="26" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="E48" s="16">
         <v>46359</v>
@@ -3373,7 +3614,7 @@
         <v>46373</v>
       </c>
       <c r="G48" s="18" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="H48" s="17">
         <v>46371</v>
@@ -3382,16 +3623,16 @@
         <v>46374</v>
       </c>
       <c r="J48" s="19" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="K48" s="19" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="L48" s="19" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="M48" s="19" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="N48" s="20">
         <v>-250</v>
@@ -3404,15 +3645,15 @@
       </c>
     </row>
     <row r="49" spans="1:16" ht="15">
-      <c r="A49" s="36"/>
+      <c r="A49" s="37"/>
       <c r="B49" s="13" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C49" s="13" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="D49" s="26" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="E49" s="16">
         <v>46359</v>
@@ -3421,7 +3662,7 @@
         <v>46373</v>
       </c>
       <c r="G49" s="18" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="H49" s="17">
         <v>46371</v>
@@ -3430,16 +3671,16 @@
         <v>46374</v>
       </c>
       <c r="J49" s="19" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="K49" s="19" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="L49" s="19" t="s">
-        <v>149</v>
+        <v>156</v>
       </c>
       <c r="M49" s="19" t="s">
-        <v>29</v>
+        <v>158</v>
       </c>
       <c r="N49" s="20">
         <v>-264.2456512</v>
@@ -3470,17 +3711,17 @@
       <c r="P50" s="24"/>
     </row>
     <row r="51" spans="1:16" ht="15">
-      <c r="A51" s="36">
+      <c r="A51" s="37">
         <v>11</v>
       </c>
       <c r="B51" s="13" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C51" s="13" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="D51" s="26" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="E51" s="16">
         <v>46364</v>
@@ -3489,7 +3730,7 @@
         <v>46378</v>
       </c>
       <c r="G51" s="18" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="H51" s="17">
         <v>46376</v>
@@ -3498,16 +3739,16 @@
         <v>46379</v>
       </c>
       <c r="J51" s="19" t="s">
-        <v>61</v>
+        <v>32</v>
       </c>
       <c r="K51" s="19" t="s">
-        <v>56</v>
+        <v>154</v>
       </c>
       <c r="L51" s="19" t="s">
-        <v>29</v>
+        <v>115</v>
       </c>
       <c r="M51" s="19" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="N51" s="20">
         <v>-221</v>
@@ -3520,15 +3761,15 @@
       </c>
     </row>
     <row r="52" spans="1:16" ht="15">
-      <c r="A52" s="36"/>
+      <c r="A52" s="37"/>
       <c r="B52" s="13" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C52" s="13" t="s">
-        <v>153</v>
+        <v>146</v>
       </c>
       <c r="D52" s="26" t="s">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="E52" s="16">
         <v>46364</v>
@@ -3537,7 +3778,7 @@
         <v>46378</v>
       </c>
       <c r="G52" s="18" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="H52" s="17">
         <v>46376</v>
@@ -3546,16 +3787,16 @@
         <v>46379</v>
       </c>
       <c r="J52" s="19" t="s">
-        <v>44</v>
+        <v>61</v>
       </c>
       <c r="K52" s="19" t="s">
-        <v>88</v>
+        <v>155</v>
       </c>
       <c r="L52" s="19" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="M52" s="19" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="N52" s="20">
         <v>-212</v>
@@ -3568,15 +3809,15 @@
       </c>
     </row>
     <row r="53" spans="1:16" ht="15">
-      <c r="A53" s="36"/>
+      <c r="A53" s="37"/>
       <c r="B53" s="13" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C53" s="13" t="s">
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="D53" s="26" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="E53" s="16">
         <v>46364</v>
@@ -3585,7 +3826,7 @@
         <v>46378</v>
       </c>
       <c r="G53" s="18" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="H53" s="17">
         <v>46376</v>
@@ -3594,16 +3835,16 @@
         <v>46379</v>
       </c>
       <c r="J53" s="19" t="s">
-        <v>157</v>
+        <v>39</v>
       </c>
       <c r="K53" s="19" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="L53" s="19" t="s">
-        <v>142</v>
+        <v>159</v>
       </c>
       <c r="M53" s="19" t="s">
-        <v>149</v>
+        <v>156</v>
       </c>
       <c r="N53" s="20">
         <v>-271.99507683269997</v>
@@ -3636,7 +3877,7 @@
     <row r="56" spans="1:16" ht="15">
       <c r="B56" s="13"/>
       <c r="C56" s="13"/>
-      <c r="D56" s="46"/>
+      <c r="D56" s="35"/>
       <c r="E56" s="16"/>
       <c r="F56" s="17"/>
       <c r="G56" s="18"/>
@@ -3669,7 +3910,7 @@
     <row r="59" spans="1:16" ht="15">
       <c r="B59" s="13"/>
       <c r="C59" s="13"/>
-      <c r="D59" s="46"/>
+      <c r="D59" s="35"/>
       <c r="E59" s="16"/>
       <c r="F59" s="17"/>
       <c r="G59" s="18"/>
@@ -3686,7 +3927,7 @@
     <row r="60" spans="1:16" ht="15">
       <c r="B60" s="13"/>
       <c r="C60" s="27"/>
-      <c r="D60" s="46"/>
+      <c r="D60" s="35"/>
       <c r="E60" s="16"/>
       <c r="F60" s="17"/>
       <c r="G60" s="18"/>
@@ -3702,18 +3943,6 @@
     </row>
   </sheetData>
   <mergeCells count="22">
-    <mergeCell ref="A11:A13"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="I1:I2"/>
-    <mergeCell ref="J1:M1"/>
-    <mergeCell ref="N1:P1"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="E1:G1"/>
-    <mergeCell ref="H1:H2"/>
     <mergeCell ref="A15:A16"/>
     <mergeCell ref="A39:A41"/>
     <mergeCell ref="A43:A45"/>
@@ -3724,6 +3953,18 @@
     <mergeCell ref="A27:A29"/>
     <mergeCell ref="A31:A33"/>
     <mergeCell ref="A35:A37"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:P1"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="E1:G1"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="A11:A13"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="A8:A9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -3731,7 +3972,21 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="17" operator="containsText" id="{1A0E45CE-F7AE-4D99-91A7-4F37B9FD5A27}">
+          <x14:cfRule type="containsText" priority="44" operator="containsText" id="{4FB9DF6C-0043-478D-9ED6-EFE99F22D9A1}">
+            <xm:f>NOT(ISERROR(SEARCH($D$2,A17)))</xm:f>
+            <xm:f>$D$2</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill>
+                  <bgColor rgb="FFFFFF00"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>A18:P19 A20:L20 N20:P20 A24:J24 L24:P24 A21:P23 A25:P27 A28:J28 L28:P28 A29:K29 M29:P29 A30:P34 A36:P36 A35:I35 K35:P35 A37:J37 L37:P37 A17:L17 A42:P42 A41:I41 A38:P40 K41:P41 A43:J43 L43:P43 A52:I52 A44:P50 K52:P52 A51:K51 M51:P51 A53:P54</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="containsText" priority="53" operator="containsText" id="{1A0E45CE-F7AE-4D99-91A7-4F37B9FD5A27}">
             <xm:f>NOT(ISERROR(SEARCH($D$2,A3)))</xm:f>
             <xm:f>$D$2</xm:f>
             <x14:dxf>
@@ -3742,10 +3997,10 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <xm:sqref>A3:P7 A8:F8 B9:F9 B16:I16 B57:C57 E57:P57 B56:P56</xm:sqref>
+          <xm:sqref>A3:P4 A8:F8 B9:F9 B16:I16 B56:P56 B57:C57 E57:P57 A7:I7 K7 A6:P6 A5:K5 M5:P5 N7:P7</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="9" operator="containsText" id="{949D15F9-932E-41EA-B4DC-A7B149A7FBCA}">
+          <x14:cfRule type="containsText" priority="37" operator="containsText" id="{C9F8E0B8-5BBA-4903-91BF-7F7022CD45AB}">
             <xm:f>NOT(ISERROR(SEARCH($D$2,A10)))</xm:f>
             <xm:f>$D$2</xm:f>
             <x14:dxf>
@@ -3756,11 +4011,11 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <xm:sqref>A10:P10 A13:P15 A11:I12</xm:sqref>
+          <xm:sqref>A10:P10 A13:P15 M11:P11 A11:I12 L12:P12</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="8" operator="containsText" id="{4FB9DF6C-0043-478D-9ED6-EFE99F22D9A1}">
-            <xm:f>NOT(ISERROR(SEARCH($D$2,A17)))</xm:f>
+          <x14:cfRule type="containsText" priority="41" operator="containsText" id="{67CF2A4D-9843-4437-BE02-F20BF883A04D}">
+            <xm:f>NOT(ISERROR(SEARCH($D$2,B59)))</xm:f>
             <xm:f>$D$2</xm:f>
             <x14:dxf>
               <fill>
@@ -3770,10 +4025,10 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <xm:sqref>A18:P54 A17:I17</xm:sqref>
+          <xm:sqref>B59:P60</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="11" operator="containsText" id="{6EA13ADB-3188-4884-A67E-794CFD474769}">
+          <x14:cfRule type="containsText" priority="47" operator="containsText" id="{6EA13ADB-3188-4884-A67E-794CFD474769}">
             <xm:f>NOT(ISERROR(SEARCH($D$2,G8)))</xm:f>
             <xm:f>$D$2</xm:f>
             <x14:dxf>
@@ -3784,11 +4039,11 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <xm:sqref>G8:P9</xm:sqref>
+          <xm:sqref>G8:P8 G9:I9 L9 N9:P9</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="6" operator="containsText" id="{D3EBB924-75D8-469B-8C3A-A8331CEF83C2}">
-            <xm:f>NOT(ISERROR(SEARCH($D$2,B59)))</xm:f>
+          <x14:cfRule type="containsText" priority="38" operator="containsText" id="{82203E34-7862-46AC-B05E-E4A35CE202DD}">
+            <xm:f>NOT(ISERROR(SEARCH($D$2,K16)))</xm:f>
             <xm:f>$D$2</xm:f>
             <x14:dxf>
               <fill>
@@ -3798,11 +4053,11 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <xm:sqref>B59:P59</xm:sqref>
+          <xm:sqref>K16 M16:P17</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="5" operator="containsText" id="{67CF2A4D-9843-4437-BE02-F20BF883A04D}">
-            <xm:f>NOT(ISERROR(SEARCH($D$2,B60)))</xm:f>
+          <x14:cfRule type="containsText" priority="35" operator="containsText" id="{7A12869D-8A5A-45D7-9806-FF58074815E6}">
+            <xm:f>NOT(ISERROR(SEARCH($D$2,J7)))</xm:f>
             <xm:f>$D$2</xm:f>
             <x14:dxf>
               <fill>
@@ -3812,10 +4067,94 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <xm:sqref>B60:P60</xm:sqref>
+          <xm:sqref>J7</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="4" operator="containsText" id="{9E4CEA65-8C41-4231-A737-92A79332793E}">
+          <x14:cfRule type="containsText" priority="33" operator="containsText" id="{0136F08C-2268-4A25-B04C-478D0DD6AC8D}">
+            <xm:f>NOT(ISERROR(SEARCH($D$2,L5)))</xm:f>
+            <xm:f>$D$2</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill>
+                  <bgColor rgb="FFFFFF00"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>L5</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="containsText" priority="32" operator="containsText" id="{A8E3A271-6429-46D5-B544-E349629DAF32}">
+            <xm:f>NOT(ISERROR(SEARCH($D$2,L7)))</xm:f>
+            <xm:f>$D$2</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill>
+                  <bgColor rgb="FFFFFF00"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>L7</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="containsText" priority="28" operator="containsText" id="{3D064B94-B5AC-4900-955A-5C5EC7F2E05F}">
+            <xm:f>NOT(ISERROR(SEARCH($D$2,M7)))</xm:f>
+            <xm:f>$D$2</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill>
+                  <bgColor rgb="FFFFFF00"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>M7</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="containsText" priority="26" operator="containsText" id="{8AEACA1A-35FA-4056-ACB5-7E9AD45F450A}">
+            <xm:f>NOT(ISERROR(SEARCH($D$2,J9)))</xm:f>
+            <xm:f>$D$2</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill>
+                  <bgColor rgb="FFFFFF00"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>J9</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="containsText" priority="24" operator="containsText" id="{EF0A4B3E-9E1E-4981-9E37-22F9D392BA87}">
+            <xm:f>NOT(ISERROR(SEARCH($D$2,K9)))</xm:f>
+            <xm:f>$D$2</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill>
+                  <bgColor rgb="FFFFFF00"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>K9</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="containsText" priority="22" operator="containsText" id="{E7D3905B-5431-43B8-8426-F5734F98892F}">
+            <xm:f>NOT(ISERROR(SEARCH($D$2,M9)))</xm:f>
+            <xm:f>$D$2</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill>
+                  <bgColor rgb="FFFFFF00"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>M9</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="containsText" priority="20" operator="containsText" id="{C249BFE8-3A94-4D0E-AA01-6E4B75A273CD}">
             <xm:f>NOT(ISERROR(SEARCH($D$2,J11)))</xm:f>
             <xm:f>$D$2</xm:f>
             <x14:dxf>
@@ -3826,10 +4165,80 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <xm:sqref>J11:P11</xm:sqref>
+          <xm:sqref>J11</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="3" operator="containsText" id="{97C4B32D-80E9-4D03-AA73-7C7279B2EA70}">
+          <x14:cfRule type="containsText" priority="18" operator="containsText" id="{B4A2B894-C9CF-4714-9D90-3563AAC4A110}">
+            <xm:f>NOT(ISERROR(SEARCH($D$2,K11)))</xm:f>
+            <xm:f>$D$2</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill>
+                  <bgColor rgb="FFFFFF00"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>K11</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="containsText" priority="17" operator="containsText" id="{D28C04EC-36F8-40EF-9324-721F45C3F827}">
+            <xm:f>NOT(ISERROR(SEARCH($D$2,L11)))</xm:f>
+            <xm:f>$D$2</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill>
+                  <bgColor rgb="FFFFFF00"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>L11</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="containsText" priority="16" operator="containsText" id="{D0B56464-8B43-4A95-B150-C5210C77C481}">
+            <xm:f>NOT(ISERROR(SEARCH($D$2,J12)))</xm:f>
+            <xm:f>$D$2</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill>
+                  <bgColor rgb="FFFFFF00"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>J12</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="containsText" priority="15" operator="containsText" id="{17325836-6A24-4E93-86F5-6DEC7A0CCBA3}">
+            <xm:f>NOT(ISERROR(SEARCH($D$2,K12)))</xm:f>
+            <xm:f>$D$2</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill>
+                  <bgColor rgb="FFFFFF00"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>K12</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="containsText" priority="13" operator="containsText" id="{17D6818F-E2BB-4B23-B5A4-2C6C744474B2}">
+            <xm:f>NOT(ISERROR(SEARCH($D$2,M20)))</xm:f>
+            <xm:f>$D$2</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill>
+                  <bgColor rgb="FFFFFF00"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>M20</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="containsText" priority="12" operator="containsText" id="{FFC8BB63-F08A-4287-A525-714D2E944936}">
             <xm:f>NOT(ISERROR(SEARCH($D$2,J16)))</xm:f>
             <xm:f>$D$2</xm:f>
             <x14:dxf>
@@ -3840,11 +4249,11 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <xm:sqref>J16:P16</xm:sqref>
+          <xm:sqref>J16</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="2" operator="containsText" id="{82203E34-7862-46AC-B05E-E4A35CE202DD}">
-            <xm:f>NOT(ISERROR(SEARCH($D$2,J17)))</xm:f>
+          <x14:cfRule type="containsText" priority="11" operator="containsText" id="{D460B58D-B866-4FE6-B08E-A5710BD4D7FF}">
+            <xm:f>NOT(ISERROR(SEARCH($D$2,L16)))</xm:f>
             <xm:f>$D$2</xm:f>
             <x14:dxf>
               <fill>
@@ -3854,11 +4263,11 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <xm:sqref>J17:P17</xm:sqref>
+          <xm:sqref>L16</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="1" operator="containsText" id="{C9F8E0B8-5BBA-4903-91BF-7F7022CD45AB}">
-            <xm:f>NOT(ISERROR(SEARCH($D$2,J12)))</xm:f>
+          <x14:cfRule type="containsText" priority="9" operator="containsText" id="{A77008B3-881C-4C0D-98C3-41ACC92D65C3}">
+            <xm:f>NOT(ISERROR(SEARCH($D$2,K24)))</xm:f>
             <xm:f>$D$2</xm:f>
             <x14:dxf>
               <fill>
@@ -3868,7 +4277,119 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <xm:sqref>J12:P12</xm:sqref>
+          <xm:sqref>K24</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="containsText" priority="8" operator="containsText" id="{E248F702-5273-4D20-9AE1-948F1C7201A1}">
+            <xm:f>NOT(ISERROR(SEARCH($D$2,K28)))</xm:f>
+            <xm:f>$D$2</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill>
+                  <bgColor rgb="FFFFFF00"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>K28</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="containsText" priority="7" operator="containsText" id="{6BB99260-FA55-4437-BE1D-B65E3B6CABF3}">
+            <xm:f>NOT(ISERROR(SEARCH($D$2,L29)))</xm:f>
+            <xm:f>$D$2</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill>
+                  <bgColor rgb="FFFFFF00"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>L29</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="containsText" priority="6" operator="containsText" id="{381DD207-2E10-49CC-B351-4DCEDA799EE8}">
+            <xm:f>NOT(ISERROR(SEARCH($D$2,J35)))</xm:f>
+            <xm:f>$D$2</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill>
+                  <bgColor rgb="FFFFFF00"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>J35</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="containsText" priority="5" operator="containsText" id="{27125436-CC63-42DF-82B8-F637F26C089D}">
+            <xm:f>NOT(ISERROR(SEARCH($D$2,K37)))</xm:f>
+            <xm:f>$D$2</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill>
+                  <bgColor rgb="FFFFFF00"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>K37</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="containsText" priority="4" operator="containsText" id="{BBC026E9-F17D-4B39-A38E-E8ECD9EAFD21}">
+            <xm:f>NOT(ISERROR(SEARCH($D$2,J41)))</xm:f>
+            <xm:f>$D$2</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill>
+                  <bgColor rgb="FFFFFF00"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>J41</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="containsText" priority="3" operator="containsText" id="{F313F913-CA5E-4533-AE0F-57B3668AC0E1}">
+            <xm:f>NOT(ISERROR(SEARCH($D$2,K43)))</xm:f>
+            <xm:f>$D$2</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill>
+                  <bgColor rgb="FFFFFF00"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>K43</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="containsText" priority="2" operator="containsText" id="{DC279D69-0103-45D9-B0C5-2E379B33F8AB}">
+            <xm:f>NOT(ISERROR(SEARCH($D$2,J52)))</xm:f>
+            <xm:f>$D$2</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill>
+                  <bgColor rgb="FFFFFF00"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>J52</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="containsText" priority="1" operator="containsText" id="{0124725D-55DF-4C03-87AF-409DDF1FBCF2}">
+            <xm:f>NOT(ISERROR(SEARCH($D$2,L51)))</xm:f>
+            <xm:f>$D$2</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill>
+                  <bgColor rgb="FFFFFF00"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>L51</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>
